--- a/TestFiles/Cost_Accounting_Income_Statement.xlsx
+++ b/TestFiles/Cost_Accounting_Income_Statement.xlsx
@@ -1,26 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sb108756\Desktop\Excel\src\main\resources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2641F490-DE80-4B92-AD18-ECC91F8D3C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>Total</t>
   </si>
@@ -130,7 +118,7 @@
     <t xml:space="preserve">Total Report Net Income: </t>
   </si>
   <si>
-    <t>Printed on: 01/29/2026</t>
+    <t>Printed on: 02/05/2026</t>
   </si>
   <si>
     <t>Page 1</t>
@@ -139,16 +127,46 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="\ mmm\ yy"/>
+    <numFmt numFmtId="165" formatCode="#,##0_);(#,##0)"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="ARIAL"/>
+      <family val="0"/>
       <charset val="1"/>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="ARIAL"/>
+      <family val="0"/>
+      <charset val="1"/>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="ARIAL"/>
+      <family val="0"/>
+      <charset val="1"/>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="ARIAL"/>
+      <family val="0"/>
+      <charset val="1"/>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="ARIAL"/>
+      <family val="0"/>
+      <charset val="1"/>
+      <color rgb="00000000"/>
     </font>
   </fonts>
   <fills count="2">
@@ -156,375 +174,111 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor rgb="00000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="top"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0">
+      <alignment indent="0" shrinkToFit="false" wrapText="false" textRotation="0" readingOrder="0" vertical="top" horizontal="general"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<file path=xl/worksheets/Sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultColWidth="6.85546875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="6.86" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="41" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="16384" width="6.86" style="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="12.75" customHeight="1" outlineLevel="0">
       <c r="A1" s="1">
         <v>38078</v>
       </c>
@@ -561,1412 +315,1409 @@
       <c r="L1" s="1">
         <v>38412</v>
       </c>
-      <c r="M1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="M1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="5" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>111383</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>108570</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>109877</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="3">
         <v>120083</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="3">
         <v>118195</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="3">
         <v>109917</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="3">
         <v>110801</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="3">
         <v>103649</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="3">
         <v>112007</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="3">
         <v>121650</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="3">
         <v>116266</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="3">
         <v>135594</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5" s="3">
         <v>1377992</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="6" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>98</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>95</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>94</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="3">
         <v>103</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="3">
         <v>102</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="3">
         <v>94</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="3">
         <v>95</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="3">
         <v>89</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="3">
         <v>96</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="3">
         <v>105</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="3">
         <v>100</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="3">
         <v>117</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="3">
         <v>1188</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+    <row r="7" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="3">
         <v>75</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>73</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>72</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="3">
         <v>79</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="3">
         <v>78</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="3">
         <v>72</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="3">
         <v>73</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="3">
         <v>68</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="3">
         <v>74</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="3">
         <v>80</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="3">
         <v>77</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="3">
         <v>91</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="3">
         <v>912</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="8" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="3">
         <v>727</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="3">
         <v>708</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <v>700</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="3">
         <v>766</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="3">
         <v>754</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="3">
         <v>700</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="3">
         <v>706</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="3">
         <v>659</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="3">
         <v>714</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="3">
         <v>777</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="3">
         <v>741</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="3">
         <v>868</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N8" s="3">
         <v>8820</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="9" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="3">
         <v>15</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>14</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <v>14</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="3">
         <v>16</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="3">
         <v>15</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="3">
         <v>14</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="3">
         <v>14</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="3">
         <v>13</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="3">
         <v>15</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="3">
         <v>16</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="3">
         <v>15</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="3">
         <v>19</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="3">
         <v>180</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    <row r="10" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="3">
         <v>13001</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>12673</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="3">
         <v>12518</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="3">
         <v>13710</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="3">
         <v>13489</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="3">
         <v>12523</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="3">
         <v>12626</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="3">
         <v>11791</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="3">
         <v>12767</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="3">
         <v>13892</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="3">
         <v>13264</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="3">
         <v>15521</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="3">
         <v>157775</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+    <row r="11" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="3">
         <v>307</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>300</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="3">
         <v>296</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="3">
         <v>324</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="3">
         <v>319</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="3">
         <v>296</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="3">
         <v>299</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="3">
         <v>279</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="3">
         <v>302</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="3">
         <v>329</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="3">
         <v>314</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M11" s="3">
         <v>366</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N11" s="3">
         <v>3731</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+    <row r="12" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="3">
         <v>48</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>48</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="3">
         <v>48</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="3">
         <v>48</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="3">
         <v>48</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="3">
         <v>48</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="3">
         <v>48</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="3">
         <v>48</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="3">
         <v>48</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="3">
         <v>48</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="3">
         <v>48</v>
       </c>
-      <c r="M12" s="2">
+      <c r="M12" s="3">
         <v>47</v>
       </c>
-      <c r="N12" s="2">
+      <c r="N12" s="3">
         <v>575</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+    <row r="13" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="3">
         <v>6439</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="3">
         <v>6439</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="3">
         <v>6439</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="3">
         <v>6439</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="3">
         <v>6439</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="3">
         <v>6439</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="3">
         <v>6439</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="3">
         <v>6439</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="3">
         <v>6439</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" s="3">
         <v>6439</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L13" s="3">
         <v>6439</v>
       </c>
-      <c r="M13" s="2">
+      <c r="M13" s="3">
         <v>6439</v>
       </c>
-      <c r="N13" s="2">
+      <c r="N13" s="3">
         <v>77268</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+    <row r="14" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="3">
         <v>793</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="3">
         <v>793</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="3">
         <v>793</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="3">
         <v>793</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="3">
         <v>793</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="3">
         <v>793</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="3">
         <v>793</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="3">
         <v>793</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="3">
         <v>793</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14" s="3">
         <v>793</v>
       </c>
-      <c r="L14" s="2">
+      <c r="L14" s="3">
         <v>793</v>
       </c>
-      <c r="M14" s="2">
+      <c r="M14" s="3">
         <v>798</v>
       </c>
-      <c r="N14" s="2">
+      <c r="N14" s="3">
         <v>9521</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+    <row r="15" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="3">
         <v>90</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="3">
         <v>90</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="3">
         <v>90</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="3">
         <v>90</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="3">
         <v>90</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="3">
         <v>90</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="3">
         <v>90</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="3">
         <v>90</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="3">
         <v>90</v>
       </c>
-      <c r="K15" s="2">
+      <c r="K15" s="3">
         <v>90</v>
       </c>
-      <c r="L15" s="2">
+      <c r="L15" s="3">
         <v>90</v>
       </c>
-      <c r="M15" s="2">
+      <c r="M15" s="3">
         <v>95</v>
       </c>
-      <c r="N15" s="2">
+      <c r="N15" s="3">
         <v>1085</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+    <row r="16" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="3">
         <v>308</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="3">
         <v>308</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="3">
         <v>308</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="3">
         <v>308</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="3">
         <v>308</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="3">
         <v>308</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="3">
         <v>308</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="3">
         <v>308</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="3">
         <v>308</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16" s="3">
         <v>308</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16" s="3">
         <v>308</v>
       </c>
-      <c r="M16" s="2">
+      <c r="M16" s="3">
         <v>308</v>
       </c>
-      <c r="N16" s="2">
+      <c r="N16" s="3">
         <v>3696</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+    <row r="17" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="3">
         <v>127</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="3">
         <v>124</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="3">
         <v>122</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="3">
         <v>134</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="3">
         <v>132</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="3">
         <v>122</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="3">
         <v>123</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="3">
         <v>115</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="3">
         <v>125</v>
       </c>
-      <c r="K17" s="2">
+      <c r="K17" s="3">
         <v>136</v>
       </c>
-      <c r="L17" s="2">
+      <c r="L17" s="3">
         <v>130</v>
       </c>
-      <c r="M17" s="2">
+      <c r="M17" s="3">
         <v>153</v>
       </c>
-      <c r="N17" s="2">
+      <c r="N17" s="3">
         <v>1543</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+    <row r="18" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="3">
         <v>116</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="3">
         <v>116</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="3">
         <v>116</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="3">
         <v>116</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="3">
         <v>116</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="3">
         <v>116</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="3">
         <v>116</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" s="3">
         <v>116</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="3">
         <v>116</v>
       </c>
-      <c r="K18" s="2">
+      <c r="K18" s="3">
         <v>116</v>
       </c>
-      <c r="L18" s="2">
+      <c r="L18" s="3">
         <v>116</v>
       </c>
-      <c r="M18" s="2">
+      <c r="M18" s="3">
         <v>116</v>
       </c>
-      <c r="N18" s="2">
+      <c r="N18" s="3">
         <v>1392</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+    <row r="19" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="3">
         <v>293</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="3">
         <v>293</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="3">
         <v>293</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="3">
         <v>293</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="3">
         <v>293</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="3">
         <v>293</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="3">
         <v>293</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19" s="3">
         <v>293</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="3">
         <v>293</v>
       </c>
-      <c r="K19" s="2">
+      <c r="K19" s="3">
         <v>293</v>
       </c>
-      <c r="L19" s="2">
+      <c r="L19" s="3">
         <v>293</v>
       </c>
-      <c r="M19" s="2">
+      <c r="M19" s="3">
         <v>293</v>
       </c>
-      <c r="N19" s="2">
+      <c r="N19" s="3">
         <v>3516</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+    <row r="20" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="3">
         <v>222</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="3">
         <v>222</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="3">
         <v>222</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="3">
         <v>222</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="3">
         <v>222</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="3">
         <v>222</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="3">
         <v>222</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20" s="3">
         <v>222</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J20" s="3">
         <v>222</v>
       </c>
-      <c r="K20" s="2">
+      <c r="K20" s="3">
         <v>222</v>
       </c>
-      <c r="L20" s="2">
+      <c r="L20" s="3">
         <v>222</v>
       </c>
-      <c r="M20" s="2">
+      <c r="M20" s="3">
         <v>218</v>
       </c>
-      <c r="N20" s="2">
+      <c r="N20" s="3">
         <v>2660</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+    <row r="21" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="3">
         <v>25</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="3">
         <v>25</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="3">
         <v>25</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="3">
         <v>25</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="3">
         <v>25</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="3">
         <v>25</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="3">
         <v>25</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I21" s="3">
         <v>25</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" s="3">
         <v>25</v>
       </c>
-      <c r="K21" s="2">
+      <c r="K21" s="3">
         <v>25</v>
       </c>
-      <c r="L21" s="2">
+      <c r="L21" s="3">
         <v>25</v>
       </c>
-      <c r="M21" s="2">
+      <c r="M21" s="3">
         <v>25</v>
       </c>
-      <c r="N21" s="2">
+      <c r="N21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+    <row r="22" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="2">
-        <v>0</v>
-      </c>
-      <c r="C22" s="2">
-        <v>0</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2">
-        <v>0</v>
-      </c>
-      <c r="K22" s="2">
-        <v>0</v>
-      </c>
-      <c r="L22" s="2">
+      <c r="B22" s="3">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>543</v>
       </c>
-      <c r="M22" s="2">
+      <c r="M22" s="3">
         <v>1737</v>
       </c>
-      <c r="N22" s="2">
+      <c r="N22" s="3">
         <v>2280</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+    <row r="23" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="3">
         <v>1840</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="3">
         <v>1840</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="3">
         <v>1840</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="3">
         <v>1840</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="3">
         <v>1840</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G23" s="3">
         <v>1840</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="3">
         <v>1840</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" s="3">
         <v>1840</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J23" s="3">
         <v>1840</v>
       </c>
-      <c r="K23" s="2">
+      <c r="K23" s="3">
         <v>1840</v>
       </c>
-      <c r="L23" s="2">
+      <c r="L23" s="3">
         <v>1840</v>
       </c>
-      <c r="M23" s="2">
+      <c r="M23" s="3">
         <v>1839</v>
       </c>
-      <c r="N23" s="2">
+      <c r="N23" s="3">
         <v>22079</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+    <row r="24" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="3">
         <v>1051</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="3">
         <v>275</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="3">
         <v>328</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="3">
         <v>2096</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="3">
         <v>40</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24" s="3">
         <v>1147</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="3">
         <v>1791</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24" s="3">
         <v>108</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J24" s="3">
         <v>1630</v>
       </c>
-      <c r="K24" s="2">
+      <c r="K24" s="3">
         <v>3445</v>
       </c>
-      <c r="L24" s="2">
+      <c r="L24" s="3">
         <v>4814</v>
       </c>
-      <c r="M24" s="2">
+      <c r="M24" s="3">
         <v>2559</v>
       </c>
-      <c r="N24" s="2">
+      <c r="N24" s="3">
         <v>19284</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+    <row r="25" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="3">
         <v>68</v>
       </c>
-      <c r="C25" s="2">
-        <v>0</v>
-      </c>
-      <c r="D25" s="2">
-        <v>0</v>
-      </c>
-      <c r="E25" s="2">
+      <c r="C25" s="3">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3">
         <v>154</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="3">
         <v>155</v>
       </c>
-      <c r="G25" s="2">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2">
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
         <v>-21</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25" s="3">
         <v>33</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="3">
         <v>115</v>
       </c>
-      <c r="K25" s="2">
+      <c r="K25" s="3">
         <v>99</v>
       </c>
-      <c r="L25" s="2">
+      <c r="L25" s="3">
         <v>42</v>
       </c>
-      <c r="M25" s="2">
+      <c r="M25" s="3">
         <v>54</v>
       </c>
-      <c r="N25" s="2">
+      <c r="N25" s="3">
         <v>699</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+    <row r="26" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="3">
         <v>-2519</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="3">
         <v>-6146</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="3">
         <v>4470</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="3">
         <v>429</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="3">
         <v>165</v>
       </c>
-      <c r="G26" s="2">
-        <v>0</v>
-      </c>
-      <c r="H26" s="2">
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>1482</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I26" s="3">
         <v>2661</v>
       </c>
-      <c r="J26" s="2">
-        <v>0</v>
-      </c>
-      <c r="K26" s="2">
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <v>704</v>
       </c>
-      <c r="L26" s="2">
-        <v>0</v>
-      </c>
-      <c r="M26" s="2">
+      <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
         <v>23</v>
       </c>
-      <c r="N26" s="2">
+      <c r="N26" s="3">
         <v>1269</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+    <row r="27" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="2">
-        <v>0</v>
-      </c>
-      <c r="C27" s="2">
-        <v>0</v>
-      </c>
-      <c r="D27" s="2">
+      <c r="B27" s="3">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3">
         <v>98</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="3">
         <v>53</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="3">
         <v>10</v>
       </c>
-      <c r="G27" s="2">
+      <c r="G27" s="3">
         <v>524</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="3">
         <v>141</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I27" s="3">
         <v>124</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J27" s="3">
         <v>204</v>
       </c>
-      <c r="K27" s="2">
+      <c r="K27" s="3">
         <v>-312</v>
       </c>
-      <c r="L27" s="2">
+      <c r="L27" s="3">
         <v>37</v>
       </c>
-      <c r="M27" s="2">
+      <c r="M27" s="3">
         <v>6</v>
       </c>
-      <c r="N27" s="2">
+      <c r="N27" s="3">
         <v>885</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+    <row r="28" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="2">
-        <v>0</v>
-      </c>
-      <c r="C28" s="2">
-        <v>0</v>
-      </c>
-      <c r="D28" s="2">
-        <v>0</v>
-      </c>
-      <c r="E28" s="2">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2">
-        <v>0</v>
-      </c>
-      <c r="G28" s="2">
-        <v>0</v>
-      </c>
-      <c r="H28" s="2">
+      <c r="B28" s="3">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
         <v>123</v>
       </c>
-      <c r="I28" s="2">
-        <v>0</v>
-      </c>
-      <c r="J28" s="2">
-        <v>0</v>
-      </c>
-      <c r="K28" s="2">
+      <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
         <v>234</v>
       </c>
-      <c r="L28" s="2">
-        <v>0</v>
-      </c>
-      <c r="M28" s="2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
         <v>262</v>
       </c>
-      <c r="N28" s="2">
+      <c r="N28" s="3">
         <v>619</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+    <row r="29" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="2">
-        <v>0</v>
-      </c>
-      <c r="C29" s="2">
-        <v>0</v>
-      </c>
-      <c r="D29" s="2">
-        <v>0</v>
-      </c>
-      <c r="E29" s="2">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2">
-        <v>0</v>
-      </c>
-      <c r="H29" s="2">
+      <c r="B29" s="3">
+        <v>0</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>336</v>
       </c>
-      <c r="I29" s="2">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2">
-        <v>0</v>
-      </c>
-      <c r="K29" s="2">
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>259</v>
       </c>
-      <c r="L29" s="2">
+      <c r="L29" s="3">
         <v>237</v>
       </c>
-      <c r="M29" s="2">
-        <v>0</v>
-      </c>
-      <c r="N29" s="2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>832</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+    <row r="30" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A30" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="2">
-        <v>0</v>
-      </c>
-      <c r="C30" s="2">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2">
-        <v>0</v>
-      </c>
-      <c r="E30" s="2">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2">
+      <c r="B30" s="3">
+        <v>0</v>
+      </c>
+      <c r="C30" s="3">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3">
         <v>-28396</v>
       </c>
-      <c r="G30" s="2">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2">
+      <c r="G30" s="3">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3">
         <v>-1151</v>
       </c>
-      <c r="I30" s="2">
+      <c r="I30" s="3">
         <v>-699</v>
       </c>
-      <c r="J30" s="2">
-        <v>0</v>
-      </c>
-      <c r="K30" s="2">
+      <c r="J30" s="3">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3">
         <v>-14586</v>
       </c>
-      <c r="L30" s="2">
+      <c r="L30" s="3">
         <v>-4539</v>
       </c>
-      <c r="M30" s="2">
+      <c r="M30" s="3">
         <v>-19129</v>
       </c>
-      <c r="N30" s="2">
+      <c r="N30" s="3">
         <v>-68500</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+    <row r="31" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="3">
         <v>2164</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="3">
         <v>875</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="3">
         <v>4787</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="3">
         <v>709</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="3">
         <v>17155</v>
       </c>
-      <c r="G31" s="2">
+      <c r="G31" s="3">
         <v>2594</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31" s="3">
         <v>2187</v>
       </c>
-      <c r="I31" s="2">
+      <c r="I31" s="3">
         <v>4287</v>
       </c>
-      <c r="J31" s="2">
+      <c r="J31" s="3">
         <v>5153</v>
       </c>
-      <c r="K31" s="2">
+      <c r="K31" s="3">
         <v>6141</v>
       </c>
-      <c r="L31" s="2">
+      <c r="L31" s="3">
         <v>17800</v>
       </c>
-      <c r="M31" s="2">
+      <c r="M31" s="3">
         <v>4648</v>
       </c>
-      <c r="N31" s="2">
+      <c r="N31" s="3">
         <v>68500</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+    <row r="32" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A32" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="3">
         <v>136671</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="3">
         <v>127735</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="3">
         <v>143550</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32" s="3">
         <v>148830</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="3">
         <v>132387</v>
       </c>
-      <c r="G32" s="2">
+      <c r="G32" s="3">
         <v>138177</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32" s="3">
         <v>139799</v>
       </c>
-      <c r="I32" s="2">
+      <c r="I32" s="3">
         <v>133351</v>
       </c>
-      <c r="J32" s="2">
+      <c r="J32" s="3">
         <v>143376</v>
       </c>
-      <c r="K32" s="2">
+      <c r="K32" s="3">
         <v>143143</v>
       </c>
-      <c r="L32" s="2">
+      <c r="L32" s="3">
         <v>160015</v>
       </c>
-      <c r="M32" s="2">
+      <c r="M32" s="3">
         <v>153067</v>
       </c>
-      <c r="N32" s="2">
+      <c r="N32" s="3">
         <v>1700101</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+    <row r="33" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A33" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+    <row r="34" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A34" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="3">
         <v>-136671</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="3">
         <v>-127735</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="3">
         <v>-143550</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E34" s="3">
         <v>-148830</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="3">
         <v>-132387</v>
       </c>
-      <c r="G34" s="2">
+      <c r="G34" s="3">
         <v>-138177</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34" s="3">
         <v>-139799</v>
       </c>
-      <c r="I34" s="2">
+      <c r="I34" s="3">
         <v>-133351</v>
       </c>
-      <c r="J34" s="2">
+      <c r="J34" s="3">
         <v>-143376</v>
       </c>
-      <c r="K34" s="2">
+      <c r="K34" s="3">
         <v>-143143</v>
       </c>
-      <c r="L34" s="2">
+      <c r="L34" s="3">
         <v>-160015</v>
       </c>
-      <c r="M34" s="2">
+      <c r="M34" s="3">
         <v>-153067</v>
       </c>
-      <c r="N34" s="2">
+      <c r="N34" s="3">
         <v>-1700101</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+    <row r="36" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A36" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="3">
         <v>-136671</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="3">
         <v>-127735</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="3">
         <v>-143550</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="3">
         <v>-148830</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="3">
         <v>-132387</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G36" s="3">
         <v>-138177</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H36" s="3">
         <v>-139799</v>
       </c>
-      <c r="I36" s="2">
+      <c r="I36" s="3">
         <v>-133351</v>
       </c>
-      <c r="J36" s="2">
+      <c r="J36" s="3">
         <v>-143376</v>
       </c>
-      <c r="K36" s="2">
+      <c r="K36" s="3">
         <v>-143143</v>
       </c>
-      <c r="L36" s="2">
+      <c r="L36" s="3">
         <v>-160015</v>
       </c>
-      <c r="M36" s="2">
+      <c r="M36" s="3">
         <v>-153067</v>
       </c>
-      <c r="N36" s="2">
+      <c r="N36" s="3">
         <v>-1700101</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+    <row r="37" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A37" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+    <row r="38" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A38" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="3">
         <v>-136671</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="3">
         <v>-127735</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="3">
         <v>-143550</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="3">
         <v>-148830</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="3">
         <v>-132387</v>
       </c>
-      <c r="G38" s="2">
+      <c r="G38" s="3">
         <v>-138177</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H38" s="3">
         <v>-139799</v>
       </c>
-      <c r="I38" s="2">
+      <c r="I38" s="3">
         <v>-133351</v>
       </c>
-      <c r="J38" s="2">
+      <c r="J38" s="3">
         <v>-143376</v>
       </c>
-      <c r="K38" s="2">
+      <c r="K38" s="3">
         <v>-143143</v>
       </c>
-      <c r="L38" s="2">
+      <c r="L38" s="3">
         <v>-160015</v>
       </c>
-      <c r="M38" s="2">
+      <c r="M38" s="3">
         <v>-153067</v>
       </c>
-      <c r="N38" s="2">
+      <c r="N38" s="3">
         <v>-1700101</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+    <row r="40" ht="12.75" customHeight="1" outlineLevel="0">
+      <c r="A40" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2" t="s">
         <v>37</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup fitToWidth="0" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" copies="0"/>
-  <ignoredErrors>
-    <ignoredError sqref="A20" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <pageSetup paperSize="1" scale="100" fitToWidth="0" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>